--- a/config/excel/CfgCombatTimelineNodes.xlsx
+++ b/config/excel/CfgCombatTimelineNodes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatTimelineNodes" sheetId="1" r:id="R805e04b726644d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatTimelineNodes" sheetId="1" r:id="Rf3c76ee9c98144cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+  </x:numFmts>
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,8 +31,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +52,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -58,7 +96,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -80,6 +118,36 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -291,143 +359,283 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>SkillID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>Tick</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>EffectIDs</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="17" t="str">
         <x:v>int[]</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="18" t="str">
         <x:v># 时间轴节点编号。</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="18" t="str">
         <x:v>所属战斗技能。</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="18" t="str">
         <x:v>施法开始后的相对逻辑帧。</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="18" t="str">
         <x:v>本节点按数组顺序执行的效果编号。</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="3" t="n">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="n">
+      <x:c r="B4" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="n">
+      <x:c r="C4" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="15" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="3" t="n">
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="n">
+      <x:c r="B5" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="n">
+      <x:c r="C5" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="str">
+      <x:c r="D5" s="15" t="str">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="3" t="n">
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="n">
+      <x:c r="B6" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="n">
+      <x:c r="C6" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="str">
+      <x:c r="D6" s="15" t="str">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="3" t="n">
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="3" t="n">
+      <x:c r="B7" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="n">
+      <x:c r="C7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="3" t="str">
+      <x:c r="D7" s="15" t="str">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="3" t="n">
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="n">
+      <x:c r="B8" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="n">
+      <x:c r="C8" s="14" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="str">
+      <x:c r="D8" s="15" t="str">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="3" t="n">
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B9" s="3" t="n">
+      <x:c r="B9" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="n">
+      <x:c r="C9" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="str">
+      <x:c r="D9" s="15" t="str">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="3" t="n">
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="14" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B10" s="3" t="n">
+      <x:c r="B10" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="n">
+      <x:c r="C10" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D10" s="3" t="str">
+      <x:c r="D10" s="15" t="str">
         <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="str">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="str">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="14" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="str">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="str">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="14" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="str">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="str">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="36" customHeight="1">
+      <x:c r="A19" s="14" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="str">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" s="14" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="str">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgCombatTimelineNodes.xlsx
+++ b/config/excel/CfgCombatTimelineNodes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatTimelineNodes" sheetId="1" r:id="Rf3c76ee9c98144cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatTimelineNodes" sheetId="1" r:id="R9244e43ce63046e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -36,6 +36,11 @@
       <x:color rgb="FF215E99"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
   <x:fills count="11">
     <x:fill>
@@ -96,7 +101,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -150,6 +155,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -638,6 +644,76 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="19" t="str">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="str">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="str">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="19" t="str">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="36" customHeight="1">
+      <x:c r="A25" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D25" s="19" t="str">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
